--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1749,6 +1749,118 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125581117</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95503</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stormyrbergets nordsluttning mot Omne, Nordingrå, Stormyrbergets nordsluttning mot Omne, Nordingrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>669156</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6983823</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,12 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95557</v>
+        <v>95564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95564</v>
+        <v>95567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95567</v>
+        <v>95571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95571</v>
+        <v>95572</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95572</v>
+        <v>95574</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95574</v>
+        <v>95576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1754,7 +1754,7 @@
         <v>125581117</v>
       </c>
       <c r="B11" t="n">
-        <v>95576</v>
+        <v>95578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43006-2023 artfynd.xlsx
+++ b/artfynd/A 43006-2023 artfynd.xlsx
@@ -1861,7 +1861,7 @@
         <v>126883103</v>
       </c>
       <c r="B12" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
